--- a/public/xlsx/cardviewtemplate.xlsx
+++ b/public/xlsx/cardviewtemplate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fujimura\laravelproject\binder\public\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7DBDCC2-5180-445C-BE2A-3D619A4DD9D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37B3A530-B87F-4962-AF0A-0EACC407D384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>作成日時：</t>
   </si>
@@ -72,6 +72,73 @@
     <t>会社名カナ</t>
     <rPh sb="0" eb="3">
       <t>カイシャメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署</t>
+    <rPh sb="0" eb="2">
+      <t>ブショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>役職</t>
+    <rPh sb="0" eb="2">
+      <t>ヤクショク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>拠点</t>
+    <rPh sb="0" eb="2">
+      <t>キョテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>拠点所在地</t>
+    <rPh sb="0" eb="5">
+      <t>キョテンショザイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>電話番号</t>
+    <rPh sb="0" eb="4">
+      <t>デンワバンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FAX番号</t>
+    <rPh sb="3" eb="5">
+      <t>バンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>携帯電話番号</t>
+    <rPh sb="0" eb="6">
+      <t>ケイタイデンワバンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールアドレス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録日</t>
+    <rPh sb="0" eb="3">
+      <t>トウロクビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>更新日</t>
+    <rPh sb="0" eb="3">
+      <t>コウシンビ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -493,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="21.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="11.25" style="2" customWidth="1"/>
@@ -503,7 +570,7 @@
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="E1" s="3" t="s">
         <v>1</v>
@@ -514,10 +581,10 @@
       </c>
       <c r="J1" s="2">
         <f ca="1">TODAY()</f>
-        <v>45884</v>
+        <v>45887</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -530,8 +597,38 @@
       <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="3" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="4"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
@@ -542,11 +639,11 @@
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
     </row>
-    <row r="4" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
     </row>
-    <row r="5" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
     </row>

--- a/public/xlsx/cardviewtemplate.xlsx
+++ b/public/xlsx/cardviewtemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fujimura\laravelproject\binder\public\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37B3A530-B87F-4962-AF0A-0EACC407D384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A09DF84-77BD-480B-96B2-D312EF55EE8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -147,10 +147,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="5" formatCode="&quot;¥&quot;#,##0;&quot;¥&quot;\-#,##0"/>
-    <numFmt numFmtId="176" formatCode="#,##0_ "/>
-  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -203,23 +199,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="5" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -560,28 +550,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="21.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="2" customWidth="1"/>
-    <col min="2" max="2" width="11.25" style="5" customWidth="1"/>
-    <col min="3" max="10" width="11.25" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.75" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="1" max="10" width="11.25" style="2" customWidth="1"/>
+    <col min="11" max="11" width="10.75" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1"/>
       <c r="E1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="3"/>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="2">
+      <c r="J1" s="1">
         <f ca="1">TODAY()</f>
-        <v>45887</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -594,58 +581,39 @@
       <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-    </row>
-    <row r="4" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-    </row>
-    <row r="5" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
